--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_la araucania.xlsx
@@ -102,12 +102,12 @@
     <t xml:space="preserve">Lautaro</t>
   </si>
   <si>
+    <t xml:space="preserve">Padre Las Casas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ercilla</t>
   </si>
   <si>
-    <t xml:space="preserve">Padre Las Casas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Villarrica</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:31</t>
+    <t xml:space="preserve">2026-09-09 23:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -945,7 +945,7 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>9204</v>
+        <v>9112</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2018</v>
@@ -962,7 +962,7 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>9112</v>
+        <v>9204</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2018</v>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:28</t>
+    <t xml:space="preserve">2026-09-17 14:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:23</t>
+    <t xml:space="preserve">2026-09-23 12:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_la araucania.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:51</t>
+    <t xml:space="preserve">2026-10-01 23:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -159,7 +159,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre salario mínimo (%)</t>
+    <t xml:space="preserve">% con ingreso igual al mínimo</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -172,9 +172,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre salario mínimo</t>
   </si>
 </sst>
 </file>
@@ -1184,7 +1181,7 @@
         <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:15</t>
+    <t xml:space="preserve">2026-10-02 11:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:23</t>
+    <t xml:space="preserve">2026-10-02 13:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:56</t>
+    <t xml:space="preserve">2026-10-05 12:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
